--- a/Data/testDataCZ_IDGenerator.xlsx
+++ b/Data/testDataCZ_IDGenerator.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD38892-1FA1-4BF2-82FF-10D32E6D17EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2C4F7A-671C-4E61-8105-3A964C070A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5278,10 +5300,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C159E3-9686-4598-8355-985D37798D7D}">
-  <dimension ref="A1:A82"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5684,18 +5707,233 @@
         <v>143172880</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
         <v>143162881</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
         <v>143152882</v>
       </c>
     </row>
+    <row r="83" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A83" s="19">
+        <v>143142883</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A84" s="19">
+        <v>143132884</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A85" s="19">
+        <v>143122885</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A86" s="19">
+        <v>143112886</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A87" s="19">
+        <v>143102887</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A88" s="19">
+        <v>143092888</v>
+      </c>
+      <c r="L88" cm="1">
+        <f t="array" aca="1" ref="L88:L102" ca="1">_xlfn.RANDARRAY(15,1,123456789,999999999,TRUE)</f>
+        <v>213728321</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A89" s="19">
+        <v>143082889</v>
+      </c>
+      <c r="L89">
+        <f ca="1"/>
+        <v>434517439</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A90" s="19">
+        <v>143072890</v>
+      </c>
+      <c r="L90">
+        <f ca="1"/>
+        <v>982257361</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A91" s="19">
+        <v>143062891</v>
+      </c>
+      <c r="L91">
+        <f ca="1"/>
+        <v>391305597</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A92" s="19">
+        <v>143052892</v>
+      </c>
+      <c r="L92">
+        <f ca="1"/>
+        <v>714983360</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A93" s="19">
+        <v>143042893</v>
+      </c>
+      <c r="L93">
+        <f ca="1"/>
+        <v>804085982</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A94" s="19">
+        <v>143032894</v>
+      </c>
+      <c r="L94">
+        <f ca="1"/>
+        <v>706602395</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A95" s="19">
+        <v>143022895</v>
+      </c>
+      <c r="L95">
+        <f ca="1"/>
+        <v>449186935</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A96" s="19">
+        <v>143012896</v>
+      </c>
+      <c r="L96">
+        <f ca="1"/>
+        <v>979666539</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A97" s="19">
+        <v>143002897</v>
+      </c>
+      <c r="L97">
+        <f ca="1"/>
+        <v>737216373</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A98" s="19">
+        <v>142992898</v>
+      </c>
+      <c r="L98">
+        <f ca="1"/>
+        <v>656359965</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A99" s="19">
+        <v>142982899</v>
+      </c>
+      <c r="L99">
+        <f ca="1"/>
+        <v>436954655</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A100" s="19">
+        <v>142972900</v>
+      </c>
+      <c r="L100">
+        <f ca="1"/>
+        <v>550127133</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A101" s="19">
+        <v>142962901</v>
+      </c>
+      <c r="L101">
+        <f ca="1"/>
+        <v>536191680</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A102" s="19">
+        <v>142952902</v>
+      </c>
+      <c r="L102">
+        <f ca="1"/>
+        <v>196668211</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A103" s="19">
+        <v>142942903</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A104" s="19">
+        <v>142932904</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A105" s="19">
+        <v>142922905</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A106" s="19">
+        <v>142912906</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A107" s="19">
+        <v>142902907</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A108" s="19">
+        <v>142892908</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A109" s="19">
+        <v>142882909</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A110" s="19">
+        <v>142872910</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A111" s="19">
+        <v>142862911</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A112" s="19">
+        <v>142852912</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A113" s="19">
+        <v>142842913</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>